--- a/output/laminas_provinciales/prov_i_ingr_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:05</t>
+    <t xml:space="preserve">2026-09-09 22:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:01</t>
+    <t xml:space="preserve">2026-09-17 13:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,18 +955,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1026000.38</v>
+        <v>1104993.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1104993.88</v>
+        <v>1026000.38</v>
       </c>
     </row>
     <row r="4">
@@ -1015,68 +1015,68 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>910519.56</v>
+        <v>986483.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1026000.38</v>
+        <v>1104993.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1086265.88</v>
+        <v>1170958.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>986483.75</v>
+        <v>910519.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1104993.88</v>
+        <v>1026000.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1170958.5</v>
+        <v>1086265.88</v>
       </c>
     </row>
     <row r="8">

--- a/output/laminas_provinciales/prov_i_ingr_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:32</t>
+    <t xml:space="preserve">2026-09-25 21:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -642,7 +642,7 @@
         <v>910519.56</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>115480.82</v>
+        <v>115480.81</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>12.68</v>
@@ -734,7 +734,7 @@
         <v>904130.88</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>156594.87</v>
+        <v>156594.88</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>17.32</v>
@@ -757,7 +757,7 @@
         <v>970180.62</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>138821.26</v>
+        <v>138821.25</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>14.31</v>
@@ -849,7 +849,7 @@
         <v>986483.75</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>118510.13</v>
+        <v>118510.12</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>12.01</v>

--- a/output/laminas_provinciales/prov_i_ingr_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_los_lagos.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:34</t>
+    <t xml:space="preserve">2026-10-05 07:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -554,7 +554,7 @@
         <v>1004366</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>891048</v>
+        <v>891049</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>-5.4</v>
